--- a/tasks/finalpool/canvas-curriculum-audit/groundtruth_workspace/Curriculum_Audit.xlsx
+++ b/tasks/finalpool/canvas-curriculum-audit/groundtruth_workspace/Curriculum_Audit.xlsx
@@ -478,7 +478,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
@@ -495,7 +495,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Assignments (6/8); Quizzes (0/3); Modules (3/4)</t>
+          <t>Assignments (6/8); Quizzes (1/3); Modules (3/4)</t>
         </is>
       </c>
     </row>
